--- a/artfynd/A 25549-2026 artfynd.xlsx
+++ b/artfynd/A 25549-2026 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>122544040</v>
+        <v>122544084</v>
       </c>
       <c r="B2" t="n">
-        <v>90909</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5447</v>
+        <v>1202</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>775484</v>
+        <v>775488</v>
       </c>
       <c r="R2" t="n">
-        <v>7105511</v>
+        <v>7105494</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>122544137</v>
+        <v>122545147</v>
       </c>
       <c r="B3" t="n">
-        <v>57631</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,43 +787,34 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>O om Degersjön, Sibirienområdet, Vb</t>
+          <t>Degersjön, Vb</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>775479</v>
+        <v>775346</v>
       </c>
       <c r="R3" t="n">
-        <v>7105518</v>
+        <v>7105628</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -860,12 +841,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-10-02</t>
+          <t>2024-10-03</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -874,6 +855,7 @@
       <c r="AE3" t="b">
         <v>0</v>
       </c>
+      <c r="AF3" t="inlineStr"/>
       <c r="AG3" t="b">
         <v>0</v>
       </c>
@@ -885,7 +867,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Aron Dynesius</t>
+          <t>Noomi Berg</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -896,37 +878,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>122544398</v>
+        <v>122544040</v>
       </c>
       <c r="B4" t="n">
-        <v>78766</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>5447</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -936,10 +913,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>775443</v>
+        <v>775484</v>
       </c>
       <c r="R4" t="n">
-        <v>7105486</v>
+        <v>7105511</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,50 +979,45 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>122545147</v>
+        <v>122544398</v>
       </c>
       <c r="B5" t="n">
-        <v>92225</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Degersjön, Vb</t>
+          <t>O om Degersjön, Sibirienområdet, Vb</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>775346</v>
+        <v>775443</v>
       </c>
       <c r="R5" t="n">
-        <v>7105628</v>
+        <v>7105486</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1072,12 +1044,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2024-10-03</t>
+          <t>2024-10-02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1086,7 +1058,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1098,7 +1069,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Noomi Berg</t>
+          <t>Aron Dynesius</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1109,15 +1080,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>122544084</v>
+        <v>122544137</v>
       </c>
       <c r="B6" t="n">
-        <v>90944</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1125,34 +1091,43 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>O om Degersjön, Sibirienområdet, Vb</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>775488</v>
+        <v>775479</v>
       </c>
       <c r="R6" t="n">
-        <v>7105494</v>
+        <v>7105518</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 25549-2026 artfynd.xlsx
+++ b/artfynd/A 25549-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544084</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -875,6 +885,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122545147</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -976,6 +991,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544040</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1077,6 +1097,11 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544398</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1187,8 +1212,20 @@
           <t>Ecogain</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122544137</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>